--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/valparaiso.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/valparaiso.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>33515.41</v>
+        <v>33211.71</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>33557.2</v>
+        <v>33998.64</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>38222.95</v>
+        <v>38186.96</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>36312.53</v>
+        <v>37884.62</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>37130.21</v>
+        <v>35854.46</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>37341.92</v>
+        <v>37633.13</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>37755.97</v>
+        <v>38298.12</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1095642.44</v>
+        <v>1086862.81</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>36935.71</v>
+        <v>37065.48</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>36890</v>
+        <v>37139.79</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/valparaiso.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>544143-14-CM25</t>
+          <t>544143-11-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>33211.71</v>
+        <v>31703.34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>544143-15-CM25</t>
+          <t>544143-14-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>33998.64</v>
+        <v>33211.71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>544143-1-CM26</t>
+          <t>544143-15-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>38186.96</v>
+        <v>33998.64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>544143-2-CM26</t>
+          <t>544143-1-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>37884.62</v>
+        <v>38186.96</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>544143-4-CM26</t>
+          <t>544143-2-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>35854.46</v>
+        <v>37884.62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>544143-5-CM26</t>
+          <t>544143-4-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>37633.13</v>
+        <v>35854.46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>544143-6-CM26</t>
+          <t>544143-5-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>38298.12</v>
+        <v>37633.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5212-57-CM26</t>
+          <t>544143-6-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -989,24 +989,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1086862.81</v>
+        <v>38298.12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>544143-7-CM26</t>
+          <t>5212-57-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1016,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1031,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1054,20 +1050,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>37065.48</v>
+        <v>1086862.81</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>544143-8-CM26</t>
+          <t>544143-7-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1122,6 +1122,67 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
+        <v>37065.48</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>544143-8-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
         <v>37139.79</v>
       </c>
     </row>

--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/valparaiso.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/valparaiso.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valparaíso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Valparaíso" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>544143-11-CM25</t>
+          <t>544143-1-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>31703.34</v>
+        <v>30183.07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>544143-14-CM25</t>
+          <t>544143-2-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>33211.71</v>
+        <v>31876.29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>544143-15-CM25</t>
+          <t>544143-3-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>33998.64</v>
+        <v>33074.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>544143-1-CM26</t>
+          <t>544143-6-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>38186.96</v>
+        <v>32668.39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>544143-2-CM26</t>
+          <t>544143-7-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>37884.62</v>
+        <v>33001.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>544143-4-CM26</t>
+          <t>3134-187-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>35854.46</v>
+        <v>58799.48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>544143-5-CM26</t>
+          <t>544143-9-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>37633.13</v>
+        <v>32929.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>544143-6-CM26</t>
+          <t>3134-257-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>38298.12</v>
+        <v>29274.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5212-57-CM26</t>
+          <t>3134-260-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1050,24 +1050,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1086862.81</v>
+        <v>67597.69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>544143-7-CM26</t>
+          <t>544143-10-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1077,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1122,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>37065.48</v>
+        <v>31494.61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>544143-8-CM26</t>
+          <t>544143-11-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1183,7 +1179,869 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
+        <v>31703.34</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5212-13-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>60.921.000-1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>923764.08</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>544143-12-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>31911.74</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>544143-13-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>32699.85</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>544143-14-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>33211.71</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>544143-15-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>33998.64</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>544143-1-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>38186.96</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>544143-2-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>37884.62</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>544143-4-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>35854.46</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>544143-5-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>37633.13</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>544143-6-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>38298.12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>5212-57-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>60.921.000-1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>1086862.81</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>544143-7-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>37065.48</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>544143-8-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
         <v>37139.79</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>544143-9-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>37448.52</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/valparaiso.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/valparaiso.xlsx
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1342,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1407,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1472,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1537,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1602,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1667,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1732,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1797,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1862,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1912,7 +1992,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1973,7 +2057,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2034,7 +2122,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/valparaiso.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -969,7 +969,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3134-257-CM25</t>
+          <t>3134-260-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>29274.59</v>
+        <v>67597.69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3134-260-CM25</t>
+          <t>3134-257-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>67597.69</v>
+        <v>29274.59</v>
       </c>
     </row>
     <row r="11">
@@ -2134,6 +2134,136 @@
       </c>
       <c r="M26" s="2" t="n">
         <v>37448.52</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>544143-11-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>35504.45</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2424-1210-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>69.061.000-0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>536058.01</v>
       </c>
     </row>
   </sheetData>
